--- a/sports_forms/009_season_play_voting_form--sports_forms.xlsx
+++ b/sports_forms/009_season_play_voting_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sports_form_category</t>
+          <t>season_category</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sports Forms</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Season Category</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Select the sport for this form</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>season_play_voting_form_description</t>
+          <t>season_description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Season Play Voting Form helps sports leagues and athletics programs collect end-of-season award votes and season feedback in one place using Jotform for fast data collection and organized form submission tracking.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Season Description</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Describe the season</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,23 +569,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>season_feedback</t>
+          <t>select_sport</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Feedback</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Select a Sport</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select one sport</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sports_form_category</t>
+          <t>select_multiple_sports</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sports Forms</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Select Multiple Sports</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select multiple sports</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -607,63 +623,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>season_play_voting_form_description</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Season Play Voting Form helps sports leagues and athletics programs collect end-of-season award votes and season feedback in one place using Jotform for fast data collection and organized form submission tracking.</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>season_feedback</t>
+          <t>season_voting_form_description</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Voting Form Description</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sports_form_category</t>
+          <t>season_feedback_description</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sports Forms</t>
+          <t>Season Feedback</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,39 +697,108 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>season_play_voting_form_description</t>
+          <t>season_audience</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Season Play Voting Form helps sports leagues and athletics programs collect end-of-season award votes and season feedback in one place using Jotform for fast data collection and organized form submission tracking.</t>
+          <t>Season Audience</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>season_feedback</t>
+          <t>season_play_audience_description</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Season Play Audience Description</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>season_feedback</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Feedback (2)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>season_play_audience_feedback</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Season Play Audience Feedback</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>season_play_audience_voting_form</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Season Play Audience Voting Form</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -733,7 +818,7 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -758,24 +843,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>season_category_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>baseball</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Baseball</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>season_category_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -792,58 +877,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>season_category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>football</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hockey</t>
+          <t>Football</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>season_category_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>soccer</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Soccer</t>
+          <t>Hockey</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>season_category_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>baseball</t>
+          <t>soccer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Baseball</t>
+          <t>Soccer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>select_sport_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -860,7 +945,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>select_sport_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -877,7 +962,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>select_sport_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -894,7 +979,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>select_sport_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -911,7 +996,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>select_sport_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -928,7 +1013,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>select_multiple_sports_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -945,7 +1030,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>select_multiple_sports_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -962,7 +1047,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>select_multiple_sports_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -979,7 +1064,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>select_multiple_sports_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -996,7 +1081,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sports_form_category_choices</t>
+          <t>select_multiple_sports_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
